--- a/research/traditional_assets/database/data/vietnam/vietnam_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ18"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2855</v>
+        <v>0.23</v>
       </c>
       <c r="E2">
-        <v>0.2955</v>
+        <v>0.151</v>
       </c>
       <c r="G2">
-        <v>0.003787060992917842</v>
+        <v>0.01016677897574124</v>
       </c>
       <c r="H2">
-        <v>0.003787060992917842</v>
+        <v>0.01016677897574124</v>
       </c>
       <c r="I2">
-        <v>0.001645068475268518</v>
+        <v>0.005366794024365974</v>
       </c>
       <c r="J2">
-        <v>0.001360084878567464</v>
+        <v>0.004466755280478317</v>
       </c>
       <c r="K2">
-        <v>454.09</v>
+        <v>395.02</v>
       </c>
       <c r="L2">
-        <v>0.4017912444565567</v>
+        <v>0.3327324797843665</v>
       </c>
       <c r="M2">
-        <v>90.899</v>
+        <v>103.258</v>
       </c>
       <c r="N2">
-        <v>0.01060739374985413</v>
+        <v>0.0273505767677169</v>
       </c>
       <c r="O2">
-        <v>0.200178378735493</v>
+        <v>0.2613994228140347</v>
       </c>
       <c r="P2">
-        <v>90.17100000000001</v>
+        <v>103.148</v>
       </c>
       <c r="Q2">
-        <v>0.01052244031087357</v>
+        <v>0.02732144039625465</v>
       </c>
       <c r="R2">
-        <v>0.1985751723226673</v>
+        <v>0.2611209559009671</v>
       </c>
       <c r="S2">
-        <v>0.7279999999999984</v>
+        <v>0.1100000000000013</v>
       </c>
       <c r="T2">
-        <v>0.008008888986677504</v>
+        <v>0.00106529276181992</v>
       </c>
       <c r="U2">
-        <v>370.593</v>
+        <v>812.603</v>
       </c>
       <c r="V2">
-        <v>0.04324608490676127</v>
+        <v>0.2152391169030686</v>
       </c>
       <c r="W2">
-        <v>0.2330345888266119</v>
+        <v>0.1362068965517241</v>
       </c>
       <c r="X2">
-        <v>0.06172035087813863</v>
+        <v>0.1225031797533433</v>
       </c>
       <c r="Y2">
-        <v>0.1713142379484733</v>
+        <v>0.01370371679838085</v>
       </c>
       <c r="Z2">
-        <v>0.3311633061333963</v>
+        <v>0.2007497777383962</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05712994820451767</v>
+        <v>0.1004920230939557</v>
       </c>
       <c r="AC2">
-        <v>-0.05626591860822117</v>
+        <v>-0.1002276077603401</v>
       </c>
       <c r="AD2">
-        <v>4086.94</v>
+        <v>3410.764</v>
       </c>
       <c r="AE2">
-        <v>26.89401415858315</v>
+        <v>22.13771067136359</v>
       </c>
       <c r="AF2">
-        <v>4113.834014158583</v>
+        <v>3432.901710671364</v>
       </c>
       <c r="AG2">
-        <v>3743.241014158583</v>
+        <v>2620.298710671364</v>
       </c>
       <c r="AH2">
-        <v>0.3243521336566223</v>
+        <v>0.4762460924594473</v>
       </c>
       <c r="AI2">
-        <v>0.6259605481797369</v>
+        <v>0.4633482592604523</v>
       </c>
       <c r="AJ2">
-        <v>0.304016092880004</v>
+        <v>0.4097002242007607</v>
       </c>
       <c r="AK2">
-        <v>0.60360825905017</v>
+        <v>0.3972377276414568</v>
       </c>
       <c r="AL2">
-        <v>1.92</v>
+        <v>20.69</v>
       </c>
       <c r="AM2">
-        <v>-16.079</v>
+        <v>-63.77800000000001</v>
       </c>
       <c r="AN2">
-        <v>366.9366133955827</v>
+        <v>176.0030961349915</v>
       </c>
       <c r="AO2">
-        <v>0.7083333333333334</v>
+        <v>0.2319961333977767</v>
       </c>
       <c r="AP2">
-        <v>336.0783815908227</v>
+        <v>135.2133087709048</v>
       </c>
       <c r="AQ2">
-        <v>-0.08458237452577896</v>
+        <v>-0.075261061808147</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Viet Dragon Securities Corporation (HOSE:VDS)</t>
+          <t>Ipa Investments Group Joint Stock Company (HNX:IPA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.5156249999999999</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.5156249999999999</v>
       </c>
       <c r="I3">
-        <v>0.007219416997659821</v>
+        <v>0.3734375</v>
       </c>
       <c r="J3">
-        <v>0.00570117050458973</v>
+        <v>0.3709593894009217</v>
       </c>
       <c r="K3">
-        <v>18.4</v>
+        <v>19.8</v>
       </c>
       <c r="L3">
-        <v>0.5242165242165242</v>
+        <v>1.546875</v>
       </c>
       <c r="M3">
-        <v>1.32</v>
+        <v>0.178</v>
       </c>
       <c r="N3">
-        <v>0.008098159509202455</v>
+        <v>0.00166510757717493</v>
       </c>
       <c r="O3">
-        <v>0.07173913043478261</v>
+        <v>0.008989898989898989</v>
       </c>
       <c r="P3">
-        <v>1.32</v>
+        <v>0.178</v>
       </c>
       <c r="Q3">
-        <v>0.008098159509202455</v>
+        <v>0.00166510757717493</v>
       </c>
       <c r="R3">
-        <v>0.07173913043478261</v>
+        <v>0.008989898989898989</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,64 +764,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.72</v>
+        <v>2.2</v>
       </c>
       <c r="V3">
-        <v>0.04122699386503068</v>
+        <v>0.0205799812909261</v>
       </c>
       <c r="X3">
-        <v>0.06630459693668986</v>
-      </c>
-      <c r="Z3">
-        <v>18.89135906566129</v>
-      </c>
-      <c r="AA3">
-        <v>0.1077028590967619</v>
+        <v>0.1624429513259506</v>
       </c>
       <c r="AB3">
-        <v>0.05890906920283127</v>
-      </c>
-      <c r="AC3">
-        <v>0.04879378989393067</v>
+        <v>0.1072009147679779</v>
       </c>
       <c r="AD3">
-        <v>98.3</v>
+        <v>192.3</v>
       </c>
       <c r="AE3">
-        <v>1.857992316910701</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>100.1579923169107</v>
+        <v>192.3</v>
       </c>
       <c r="AG3">
-        <v>93.43799231691069</v>
+        <v>190.1</v>
       </c>
       <c r="AH3">
-        <v>0.3806002296760739</v>
+        <v>0.6427139037433155</v>
       </c>
       <c r="AI3">
-        <v>0.604972257244993</v>
+        <v>0.534018328242155</v>
       </c>
       <c r="AJ3">
-        <v>0.3643687562544879</v>
+        <v>0.6400673400673401</v>
       </c>
       <c r="AK3">
-        <v>0.5882597164190095</v>
+        <v>0.5311539536183292</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>18.1</v>
       </c>
       <c r="AM3">
-        <v>-1.11</v>
+        <v>-49.2</v>
       </c>
       <c r="AN3">
-        <v>157.28</v>
+        <v>27.12270803949225</v>
+      </c>
+      <c r="AO3">
+        <v>0.2640883977900552</v>
       </c>
       <c r="AP3">
-        <v>149.5007877070571</v>
+        <v>26.81241184767278</v>
       </c>
       <c r="AQ3">
-        <v>-0</v>
+        <v>-0.09715447154471546</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F.I.T  Group  Joint Stock Company (HOSE:FIT)</t>
+          <t>Hoa Binh Securities Joint Stock Company (HNX:HBS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,29 +834,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.126</v>
-      </c>
-      <c r="E4">
-        <v>0.0341</v>
-      </c>
-      <c r="G4">
-        <v>0.07940630797773655</v>
-      </c>
-      <c r="H4">
-        <v>0.07940630797773655</v>
-      </c>
-      <c r="I4">
-        <v>0.02523191094619666</v>
-      </c>
-      <c r="J4">
-        <v>0.02095345648140679</v>
-      </c>
       <c r="K4">
-        <v>6.45</v>
-      </c>
-      <c r="L4">
-        <v>0.1196660482374768</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -870,89 +843,71 @@
       <c r="N4">
         <v>-0</v>
       </c>
-      <c r="O4">
-        <v>-0</v>
-      </c>
       <c r="P4">
         <v>-0</v>
       </c>
       <c r="Q4">
         <v>-0</v>
       </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.14</v>
+        <v>14.4</v>
       </c>
       <c r="V4">
-        <v>0.01125131440588854</v>
+        <v>1.959183673469388</v>
       </c>
       <c r="W4">
-        <v>0.0492742551566081</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.05302462780783222</v>
+        <v>0.08949199776307479</v>
       </c>
       <c r="Y4">
-        <v>-0.003750372651224125</v>
+        <v>-0.08949199776307479</v>
       </c>
       <c r="Z4">
-        <v>0.3353449884900143</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>0.007026636622583376</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05231255803506697</v>
+        <v>0.08949199776307479</v>
       </c>
       <c r="AC4">
-        <v>-0.04528592141248359</v>
+        <v>-0.08949199776307479</v>
       </c>
       <c r="AD4">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>22.76</v>
+        <v>-14.4</v>
       </c>
       <c r="AH4">
-        <v>0.1157601115760112</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.11437758383096</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.1068745304282494</v>
+        <v>2.042553191489362</v>
       </c>
       <c r="AK4">
-        <v>0.1055854518463537</v>
+        <v>-5.999999999999999</v>
       </c>
       <c r="AL4">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>-11.58</v>
-      </c>
-      <c r="AN4">
-        <v>4.733840304182509</v>
-      </c>
-      <c r="AO4">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="AP4">
-        <v>4.326996197718631</v>
-      </c>
-      <c r="AQ4">
-        <v>-0.1174438687392055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -984,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>7.53</v>
+        <v>5.53</v>
       </c>
       <c r="L5">
-        <v>0.6845454545454546</v>
+        <v>0.1498644986449865</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1011,61 +966,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>10.6</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="V5">
-        <v>0.07386759581881533</v>
+        <v>0.2800675675675675</v>
       </c>
       <c r="W5">
-        <v>0.4796178343949045</v>
+        <v>0.1362068965517241</v>
       </c>
       <c r="X5">
-        <v>0.04942926046568479</v>
+        <v>0.08975778823783252</v>
       </c>
       <c r="Y5">
-        <v>0.4301885739292197</v>
+        <v>0.04644910831389161</v>
       </c>
       <c r="Z5">
-        <v>0.7751937984496124</v>
+        <v>1.23</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04942926046568479</v>
+        <v>0.08973027086007183</v>
       </c>
       <c r="AC5">
-        <v>-0.04942926046568479</v>
+        <v>-0.08973027086007183</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="AG5">
-        <v>-10.6</v>
+        <v>-8.095999999999998</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.006511378129824797</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.004136989806798311</v>
       </c>
       <c r="AJ5">
-        <v>-0.07975921745673438</v>
+        <v>-0.3764880952380951</v>
       </c>
       <c r="AK5">
-        <v>-0.3533333333333333</v>
+        <v>-0.2097192000828929</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.116</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AQ5">
         <v>-0</v>
@@ -1079,7 +1034,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wall Street Securities Joint Stock Company (HNX:WSS)</t>
+          <t>Agribank Securities Corporation (HOSE:AGR)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1087,6 +1042,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.164</v>
+      </c>
+      <c r="E6">
+        <v>0.143</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1100,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>2.9</v>
+        <v>7.34</v>
       </c>
       <c r="L6">
-        <v>5.141843971631206</v>
+        <v>0.4421686746987951</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1127,61 +1088,64 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.426</v>
+        <v>0.623</v>
       </c>
       <c r="V6">
-        <v>0.01062344139650873</v>
+        <v>0.009188790560471977</v>
       </c>
       <c r="W6">
-        <v>0.1355140186915888</v>
+        <v>0.07153996101364522</v>
       </c>
       <c r="X6">
-        <v>0.04942926046568479</v>
+        <v>0.09122060984018729</v>
       </c>
       <c r="Y6">
-        <v>0.086084758225904</v>
+        <v>-0.01968064882654207</v>
       </c>
       <c r="Z6">
-        <v>0.02727800348229832</v>
+        <v>0.159186804756425</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04942926046568479</v>
+        <v>0.09049417010580531</v>
       </c>
       <c r="AC6">
-        <v>-0.04942926046568479</v>
+        <v>-0.09049417010580531</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AG6">
-        <v>-0.426</v>
+        <v>2.267</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.04088272740132975</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.02683628934905748</v>
       </c>
       <c r="AJ6">
-        <v>-0.01073751071230529</v>
+        <v>0.03235474617152155</v>
       </c>
       <c r="AK6">
-        <v>-0.01846233856288463</v>
+        <v>0.02117365761625898</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>-0.055</v>
+      </c>
+      <c r="AQ6">
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -1192,7 +1156,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agribank Securities Corporation (HOSE:AGR)</t>
+          <t>VIX Securities Joint Stock Company (HOSE:VIX)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1200,26 +1164,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.196</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
       <c r="K7">
-        <v>14.6</v>
-      </c>
-      <c r="L7">
-        <v>1.013888888888889</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1227,80 +1173,71 @@
       <c r="N7">
         <v>-0</v>
       </c>
-      <c r="O7">
-        <v>-0</v>
-      </c>
       <c r="P7">
         <v>-0</v>
       </c>
       <c r="Q7">
         <v>-0</v>
       </c>
-      <c r="R7">
-        <v>-0</v>
-      </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2.66</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="V7">
-        <v>0.01118116855821774</v>
+        <v>0.5342983008181246</v>
       </c>
       <c r="W7">
-        <v>0.1659090909090909</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>0.04993027430484771</v>
+        <v>0.09163069601986303</v>
       </c>
       <c r="Y7">
-        <v>0.1159788166042432</v>
+        <v>-0.09163069601986303</v>
       </c>
       <c r="Z7">
-        <v>0.1758027102917837</v>
+        <v>0</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04987550653203998</v>
+        <v>0.09072000959406794</v>
       </c>
       <c r="AC7">
-        <v>-0.04987550653203998</v>
+        <v>-0.09072000959406794</v>
       </c>
       <c r="AD7">
-        <v>4.34</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>4.34</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AG7">
-        <v>1.68</v>
+        <v>-76.52000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.01791611624834874</v>
+        <v>0.05009564801530369</v>
       </c>
       <c r="AI7">
-        <v>0.04058350476902936</v>
+        <v>0.0244900344847741</v>
       </c>
       <c r="AJ7">
-        <v>0.007012271475081391</v>
+        <v>-0.9288662296673952</v>
       </c>
       <c r="AK7">
-        <v>0.01611047180667434</v>
+        <v>-0.2974191542288558</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.063</v>
-      </c>
-      <c r="AQ7">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1311,7 +1248,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viet Capital Securities Joint Stock Company (HOSE:VCI)</t>
+          <t>Saigon - Hanoi Securities Joint Stock Company (HNX:SHS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1320,10 +1257,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.344</v>
+        <v>0.189</v>
       </c>
       <c r="E8">
-        <v>0.379</v>
+        <v>0.151</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1332,34 +1269,34 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.003591464506149156</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0.002913557551173211</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>60.6</v>
+        <v>24.7</v>
       </c>
       <c r="L8">
-        <v>0.4690402476780186</v>
+        <v>0.3130544993662864</v>
       </c>
       <c r="M8">
-        <v>21.8</v>
+        <v>10.4</v>
       </c>
       <c r="N8">
-        <v>0.02043686134808287</v>
+        <v>0.0362495643081213</v>
       </c>
       <c r="O8">
-        <v>0.3597359735973598</v>
+        <v>0.4210526315789474</v>
       </c>
       <c r="P8">
-        <v>21.8</v>
+        <v>10.4</v>
       </c>
       <c r="Q8">
-        <v>0.02043686134808287</v>
+        <v>0.0362495643081213</v>
       </c>
       <c r="R8">
-        <v>0.3597359735973598</v>
+        <v>0.4210526315789474</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1368,70 +1305,61 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>28.7</v>
+        <v>22.6</v>
       </c>
       <c r="V8">
-        <v>0.02690540920596231</v>
+        <v>0.07877309166957129</v>
       </c>
       <c r="W8">
-        <v>0.3513043478260869</v>
+        <v>0.1374513077351141</v>
       </c>
       <c r="X8">
-        <v>0.05661140168233772</v>
+        <v>0.09876462251945736</v>
       </c>
       <c r="Y8">
-        <v>0.2946929461437492</v>
+        <v>0.03868668521565671</v>
       </c>
       <c r="Z8">
-        <v>0.4911428657840189</v>
+        <v>0.2509541984732825</v>
       </c>
       <c r="AA8">
-        <v>0.001430973005309879</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05459267525303492</v>
+        <v>0.0940539136154785</v>
       </c>
       <c r="AC8">
-        <v>-0.05316170224772504</v>
+        <v>-0.0940539136154785</v>
       </c>
       <c r="AD8">
-        <v>277.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AE8">
-        <v>1.159913929027645</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>278.9599139290277</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AG8">
-        <v>250.2599139290277</v>
+        <v>42.99999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.2073034286311812</v>
+        <v>0.1860992907801418</v>
       </c>
       <c r="AI8">
-        <v>0.5008617441803451</v>
+        <v>0.1421143847487002</v>
       </c>
       <c r="AJ8">
-        <v>0.1900284976650508</v>
+        <v>0.1303425280387996</v>
       </c>
       <c r="AK8">
-        <v>0.4737439039575704</v>
+        <v>0.09794988610478358</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-0.197</v>
-      </c>
-      <c r="AN8">
-        <v>399.1379310344828</v>
-      </c>
-      <c r="AP8">
-        <v>359.5688418520513</v>
-      </c>
-      <c r="AQ8">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1442,7 +1370,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Saigon - Hanoi Securities Joint Stock Company (HNX:SHS)</t>
+          <t>SSI Securities Corporation (HOSE:SSI)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1451,10 +1379,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.382</v>
+        <v>0.235</v>
       </c>
       <c r="E9">
-        <v>0.5760000000000001</v>
+        <v>0.218</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1463,97 +1391,106 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.003641763879307881</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>0.002915107577303125</v>
       </c>
       <c r="K9">
-        <v>51.6</v>
+        <v>103.2</v>
       </c>
       <c r="L9">
-        <v>0.5175526579739218</v>
+        <v>0.3975346687211094</v>
       </c>
       <c r="M9">
-        <v>0.001</v>
+        <v>41.685</v>
       </c>
       <c r="N9">
-        <v>1.380834023750345e-06</v>
+        <v>0.03765582655826558</v>
       </c>
       <c r="O9">
-        <v>1.937984496124031e-05</v>
+        <v>0.4039244186046512</v>
       </c>
       <c r="P9">
-        <v>0.001</v>
+        <v>41.6</v>
       </c>
       <c r="Q9">
-        <v>1.380834023750345e-06</v>
+        <v>0.03757904245709124</v>
       </c>
       <c r="R9">
-        <v>1.937984496124031e-05</v>
+        <v>0.4031007751937984</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>0.08500000000000085</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.002039102794770321</v>
       </c>
       <c r="U9">
         <v>25.8</v>
       </c>
       <c r="V9">
-        <v>0.0356255178127589</v>
+        <v>0.02330623306233062</v>
       </c>
       <c r="W9">
-        <v>0.4222585924713584</v>
+        <v>0.1957882754695504</v>
       </c>
       <c r="X9">
-        <v>0.05557648291416588</v>
+        <v>0.1230145834806527</v>
       </c>
       <c r="Y9">
-        <v>0.3666821095571925</v>
+        <v>0.07277369198889766</v>
       </c>
       <c r="Z9">
-        <v>0.4214219291571562</v>
+        <v>0.1276759201616704</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>0.0003721890423024342</v>
       </c>
       <c r="AB9">
-        <v>0.05398472630933346</v>
+        <v>0.1005853157144395</v>
       </c>
       <c r="AC9">
-        <v>-0.05398472630933346</v>
+        <v>-0.1002131266721371</v>
       </c>
       <c r="AD9">
-        <v>162.1</v>
+        <v>897.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>17.97299048465837</v>
       </c>
       <c r="AF9">
-        <v>162.1</v>
+        <v>915.0729904846584</v>
       </c>
       <c r="AG9">
-        <v>136.3</v>
+        <v>889.2729904846584</v>
       </c>
       <c r="AH9">
-        <v>0.1828951822182105</v>
+        <v>0.452542017420118</v>
       </c>
       <c r="AI9">
-        <v>0.4742539496781744</v>
+        <v>0.4962776694527823</v>
       </c>
       <c r="AJ9">
-        <v>0.1583962812318419</v>
+        <v>0.4454666244163126</v>
       </c>
       <c r="AK9">
-        <v>0.4313291139240506</v>
+        <v>0.4891294217222806</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>-3.88</v>
+      </c>
+      <c r="AN9">
+        <v>197.5991189427313</v>
+      </c>
+      <c r="AP9">
+        <v>195.8751080362684</v>
+      </c>
+      <c r="AQ9">
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -1564,7 +1501,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Everest Securities Joint Stock Company (HNX:EVS)</t>
+          <t>Bao Viet Securities Joint Stock Company (HNX:BVS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1572,6 +1509,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.153</v>
+      </c>
+      <c r="E10">
+        <v>0.104</v>
+      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1585,88 +1528,91 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>6.16</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L10">
-        <v>0.3874213836477988</v>
+        <v>0.236056338028169</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>2.38</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.03808</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.2840095465393794</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.03808</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.2840095465393794</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>1.69</v>
+        <v>7.17</v>
       </c>
       <c r="V10">
-        <v>0.01434634974533107</v>
+        <v>0.11472</v>
       </c>
       <c r="W10">
-        <v>0.2053333333333333</v>
+        <v>0.09098805646036918</v>
       </c>
       <c r="X10">
-        <v>0.05716937216321101</v>
+        <v>0.1210913614886651</v>
       </c>
       <c r="Y10">
-        <v>0.1481639611701223</v>
+        <v>-0.03010330502829588</v>
       </c>
       <c r="Z10">
-        <v>0.4370533260032985</v>
+        <v>0.1860879593227447</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.05544151666120187</v>
+        <v>0.1002276077603401</v>
       </c>
       <c r="AC10">
-        <v>-0.05544151666120187</v>
+        <v>-0.1002276077603401</v>
       </c>
       <c r="AD10">
-        <v>33.2</v>
+        <v>48.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>33.2</v>
+        <v>48.7</v>
       </c>
       <c r="AG10">
-        <v>31.51</v>
+        <v>41.53</v>
       </c>
       <c r="AH10">
-        <v>0.2198675496688742</v>
+        <v>0.4379496402877698</v>
       </c>
       <c r="AI10">
-        <v>0.4450402144772119</v>
+        <v>0.3451452870304748</v>
       </c>
       <c r="AJ10">
-        <v>0.2110374388855402</v>
+        <v>0.3992117658367779</v>
       </c>
       <c r="AK10">
-        <v>0.4321766561514196</v>
+        <v>0.3100873590681699</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-0.07000000000000001</v>
+        <v>-1.95</v>
       </c>
       <c r="AQ10">
         <v>-0</v>
@@ -1680,7 +1626,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thien Viet Securities Joint Stock Company (HOSE:TVS)</t>
+          <t>F.I.T Group Joint Stock Company (HOSE:FIT)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1689,112 +1635,118 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.456</v>
+        <v>-0.00323</v>
       </c>
       <c r="E11">
-        <v>0.5600000000000001</v>
+        <v>-0.0781</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.07391891891891891</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>0.07391891891891891</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>0.0002702702702702703</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.0001871747523921437</v>
       </c>
       <c r="K11">
-        <v>21.9</v>
+        <v>2.91</v>
       </c>
       <c r="L11">
-        <v>0.5934959349593496</v>
+        <v>0.03932432432432433</v>
       </c>
       <c r="M11">
-        <v>2.602</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.009129824561403509</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.1188127853881279</v>
+        <v>-0</v>
       </c>
       <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>-0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>9.32</v>
+      </c>
+      <c r="V11">
+        <v>0.1838264299802761</v>
+      </c>
+      <c r="W11">
+        <v>0.02080057183702645</v>
+      </c>
+      <c r="X11">
+        <v>0.1221268460271134</v>
+      </c>
+      <c r="Y11">
+        <v>-0.101326274190087</v>
+      </c>
+      <c r="Z11">
+        <v>0.556558363417569</v>
+      </c>
+      <c r="AA11">
+        <v>0.0001041736738644602</v>
+      </c>
+      <c r="AB11">
+        <v>0.1004225378452536</v>
+      </c>
+      <c r="AC11">
+        <v>-0.1003183641713892</v>
+      </c>
+      <c r="AD11">
+        <v>40.8</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>40.8</v>
+      </c>
+      <c r="AG11">
+        <v>31.48</v>
+      </c>
+      <c r="AH11">
+        <v>0.4459016393442622</v>
+      </c>
+      <c r="AI11">
+        <v>0.1403991741225051</v>
+      </c>
+      <c r="AJ11">
+        <v>0.383061572158676</v>
+      </c>
+      <c r="AK11">
+        <v>0.1119169510807736</v>
+      </c>
+      <c r="AL11">
         <v>2.59</v>
       </c>
-      <c r="Q11">
-        <v>0.009087719298245613</v>
-      </c>
-      <c r="R11">
-        <v>0.1182648401826484</v>
-      </c>
-      <c r="S11">
-        <v>0.01200000000000001</v>
-      </c>
-      <c r="T11">
-        <v>0.004611837048424293</v>
-      </c>
-      <c r="U11">
-        <v>7.82</v>
-      </c>
-      <c r="V11">
-        <v>0.02743859649122807</v>
-      </c>
-      <c r="W11">
-        <v>0.4328063241106719</v>
-      </c>
-      <c r="X11">
-        <v>0.06162879555327972</v>
-      </c>
-      <c r="Y11">
-        <v>0.3711775285573922</v>
-      </c>
-      <c r="Z11">
-        <v>0.1915688921191984</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.05709032055524048</v>
-      </c>
-      <c r="AC11">
-        <v>-0.05709032055524048</v>
-      </c>
-      <c r="AD11">
-        <v>126.6</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>126.6</v>
-      </c>
-      <c r="AG11">
-        <v>118.78</v>
-      </c>
-      <c r="AH11">
-        <v>0.3075801749271136</v>
-      </c>
-      <c r="AI11">
-        <v>0.6423135464231354</v>
-      </c>
-      <c r="AJ11">
-        <v>0.2941700926246966</v>
-      </c>
-      <c r="AK11">
-        <v>0.6275359256128487</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
       <c r="AM11">
-        <v>-0.004</v>
+        <v>-7.380000000000001</v>
+      </c>
+      <c r="AN11">
+        <v>6.486486486486486</v>
+      </c>
+      <c r="AO11">
+        <v>0.007722007722007722</v>
+      </c>
+      <c r="AP11">
+        <v>5.00476947535771</v>
       </c>
       <c r="AQ11">
-        <v>-0</v>
+        <v>-0.002710027100271002</v>
       </c>
     </row>
     <row r="12">
@@ -1805,7 +1757,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VNDIRECT Securities Joint Stock Company (HOSE:VND)</t>
+          <t>Viet Capital Securities Joint Stock Company (HOSE:VCI)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1814,10 +1766,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.476</v>
+        <v>0.23</v>
       </c>
       <c r="E12">
-        <v>0.54</v>
+        <v>0.176</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1826,34 +1778,34 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>-0.002961756262055725</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>-0.002355601485018991</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>78.59999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="L12">
-        <v>0.4330578512396694</v>
+        <v>0.4349206349206349</v>
       </c>
       <c r="M12">
-        <v>4.71</v>
+        <v>16.7</v>
       </c>
       <c r="N12">
-        <v>0.00300133817625693</v>
+        <v>0.03926640018810251</v>
       </c>
       <c r="O12">
-        <v>0.05992366412213741</v>
+        <v>0.3047445255474452</v>
       </c>
       <c r="P12">
-        <v>4.71</v>
+        <v>16.7</v>
       </c>
       <c r="Q12">
-        <v>0.00300133817625693</v>
+        <v>0.03926640018810251</v>
       </c>
       <c r="R12">
-        <v>0.05992366412213741</v>
+        <v>0.3047445255474452</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1862,67 +1814,61 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>84</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="V12">
-        <v>0.05352705027719366</v>
+        <v>0.1812837996708206</v>
       </c>
       <c r="W12">
-        <v>0.5107212475633528</v>
+        <v>0.1971223021582734</v>
       </c>
       <c r="X12">
-        <v>0.06181190620299754</v>
+        <v>0.1225031797533433</v>
       </c>
       <c r="Y12">
-        <v>0.4489093413603553</v>
+        <v>0.07461912240493009</v>
       </c>
       <c r="Z12">
-        <v>0.3294311061368897</v>
+        <v>0.2390438247011953</v>
       </c>
       <c r="AA12">
-        <v>-0.0007760084028275063</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.05716957585379485</v>
+        <v>0.1004920230939557</v>
       </c>
       <c r="AC12">
-        <v>-0.05794558425662236</v>
+        <v>-0.1004920230939557</v>
       </c>
       <c r="AD12">
-        <v>704.8</v>
+        <v>346.2</v>
       </c>
       <c r="AE12">
-        <v>2.762793807815571</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>707.5627938078155</v>
+        <v>346.2</v>
       </c>
       <c r="AG12">
-        <v>623.5627938078155</v>
+        <v>269.1</v>
       </c>
       <c r="AH12">
-        <v>0.310762157356215</v>
+        <v>0.4487362281270252</v>
       </c>
       <c r="AI12">
-        <v>0.6537205434774493</v>
+        <v>0.5562339331619537</v>
       </c>
       <c r="AJ12">
-        <v>0.2843601503790507</v>
+        <v>0.3875288018433179</v>
       </c>
       <c r="AK12">
-        <v>0.6245853688412303</v>
+        <v>0.4934898221162664</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-0.438</v>
-      </c>
-      <c r="AN12">
-        <v>46986.66666666666</v>
-      </c>
-      <c r="AP12">
-        <v>41570.85292052104</v>
+        <v>-0.217</v>
       </c>
       <c r="AQ12">
         <v>-0</v>
@@ -1945,10 +1891,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.367</v>
+        <v>0.279</v>
       </c>
       <c r="E13">
-        <v>0.289</v>
+        <v>0.165</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1957,34 +1903,34 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.001443914085726347</v>
+        <v>0.004419852414923821</v>
       </c>
       <c r="J13">
-        <v>0.001157620775625433</v>
+        <v>0.003539432014200039</v>
       </c>
       <c r="K13">
-        <v>46.5</v>
+        <v>39.8</v>
       </c>
       <c r="L13">
-        <v>0.2961783439490446</v>
+        <v>0.3031226199543031</v>
       </c>
       <c r="M13">
-        <v>16.1</v>
+        <v>6.39</v>
       </c>
       <c r="N13">
-        <v>0.01762066323738645</v>
+        <v>0.01663629263212705</v>
       </c>
       <c r="O13">
-        <v>0.346236559139785</v>
+        <v>0.1605527638190955</v>
       </c>
       <c r="P13">
-        <v>16.1</v>
+        <v>6.39</v>
       </c>
       <c r="Q13">
-        <v>0.01762066323738645</v>
+        <v>0.01663629263212705</v>
       </c>
       <c r="R13">
-        <v>0.346236559139785</v>
+        <v>0.1605527638190955</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1993,67 +1939,67 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>155.1</v>
+        <v>277.2</v>
       </c>
       <c r="V13">
-        <v>0.1697493706905986</v>
+        <v>0.7216870606612861</v>
       </c>
       <c r="W13">
-        <v>0.2419354838709677</v>
+        <v>0.1770462633451957</v>
       </c>
       <c r="X13">
-        <v>0.06648715784369441</v>
+        <v>0.138544680658354</v>
       </c>
       <c r="Y13">
-        <v>0.1754483260272733</v>
+        <v>0.03850158268684173</v>
       </c>
       <c r="Z13">
-        <v>0.4701844264030067</v>
+        <v>0.2059936247416543</v>
       </c>
       <c r="AA13">
-        <v>0.0005442952603796481</v>
+        <v>0.0007291004301317205</v>
       </c>
       <c r="AB13">
-        <v>0.05897233099058704</v>
+        <v>0.1029112051427342</v>
       </c>
       <c r="AC13">
-        <v>-0.05842803573020739</v>
+        <v>-0.1021821047126025</v>
       </c>
       <c r="AD13">
-        <v>565.3</v>
+        <v>462.2</v>
       </c>
       <c r="AE13">
-        <v>2.211527442704818</v>
+        <v>2.398366889602511</v>
       </c>
       <c r="AF13">
-        <v>567.5115274427047</v>
+        <v>464.5983668896025</v>
       </c>
       <c r="AG13">
-        <v>412.4115274427047</v>
+        <v>187.3983668896025</v>
       </c>
       <c r="AH13">
-        <v>0.3831400964199267</v>
+        <v>0.5474246033868435</v>
       </c>
       <c r="AI13">
-        <v>0.7162732180288059</v>
+        <v>0.5809670072187852</v>
       </c>
       <c r="AJ13">
-        <v>0.3109930944028561</v>
+        <v>0.3279070908102921</v>
       </c>
       <c r="AK13">
-        <v>0.6472129107547996</v>
+        <v>0.3586582825228189</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-0.098</v>
+        <v>-0.123</v>
       </c>
       <c r="AN13">
-        <v>844.9925261584453</v>
+        <v>436.0377358490566</v>
       </c>
       <c r="AP13">
-        <v>616.4596822760907</v>
+        <v>176.7909121600024</v>
       </c>
       <c r="AQ13">
         <v>-0</v>
@@ -2067,7 +2013,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MB Securities Joint Stock Company (HNX:MBS)</t>
+          <t>Thien Viet Securities Joint Stock Company (HOSE:TVS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2076,7 +2022,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.297</v>
+        <v>0.26</v>
+      </c>
+      <c r="E14">
+        <v>0.0668</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2091,85 +2040,82 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>22.5</v>
+        <v>7.79</v>
       </c>
       <c r="L14">
-        <v>0.3186968838526912</v>
+        <v>0.2128415300546448</v>
       </c>
       <c r="M14">
-        <v>7.224</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.0151892346509672</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>0.3210666666666667</v>
+        <v>-0</v>
       </c>
       <c r="P14">
-        <v>7.21</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.01515979814970563</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.3204444444444444</v>
+        <v>-0</v>
       </c>
       <c r="S14">
-        <v>0.01400000000000023</v>
-      </c>
-      <c r="T14">
-        <v>0.001937984496124064</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>6.72</v>
+        <v>10.4</v>
       </c>
       <c r="V14">
-        <v>0.01412952060555088</v>
+        <v>0.09252669039145907</v>
       </c>
       <c r="W14">
-        <v>0.2659574468085106</v>
+        <v>0.1106534090909091</v>
       </c>
       <c r="X14">
-        <v>0.06664874822155897</v>
+        <v>0.1336174876308616</v>
       </c>
       <c r="Y14">
-        <v>0.1993086985869517</v>
+        <v>-0.02296407853995248</v>
       </c>
       <c r="Z14">
-        <v>0.425660195345472</v>
+        <v>0.1934665398033619</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.05902789470277886</v>
+        <v>0.102265674449063</v>
       </c>
       <c r="AC14">
-        <v>-0.05902789470277886</v>
+        <v>-0.102265674449063</v>
       </c>
       <c r="AD14">
-        <v>298.2</v>
+        <v>122.3</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>298.2</v>
+        <v>122.3</v>
       </c>
       <c r="AG14">
-        <v>291.48</v>
+        <v>111.9</v>
       </c>
       <c r="AH14">
-        <v>0.3853708968725769</v>
+        <v>0.5210907541542394</v>
       </c>
       <c r="AI14">
-        <v>0.6771117166212535</v>
+        <v>0.6236613972463029</v>
       </c>
       <c r="AJ14">
-        <v>0.3799864420920895</v>
+        <v>0.4988854213107445</v>
       </c>
       <c r="AK14">
-        <v>0.6721084670724958</v>
+        <v>0.6025848142164781</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2186,7 +2132,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BIDV Securities Joint Stock Company (HOSE:BSI)</t>
+          <t>VNDIRECT Securities Joint Stock Company (HOSE:VND)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2195,10 +2141,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.217</v>
+        <v>0.476</v>
       </c>
       <c r="E15">
-        <v>0.302</v>
+        <v>0.408</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2207,97 +2153,103 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.000175342563571548</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>0.0001407228252429791</v>
       </c>
       <c r="K15">
-        <v>13.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="L15">
-        <v>0.290948275862069</v>
+        <v>0.3370398773006135</v>
       </c>
       <c r="M15">
-        <v>4.8</v>
+        <v>25.512</v>
       </c>
       <c r="N15">
-        <v>0.02116402116402116</v>
+        <v>0.03694713975380159</v>
       </c>
       <c r="O15">
-        <v>0.3555555555555556</v>
+        <v>0.2902389078498294</v>
       </c>
       <c r="P15">
-        <v>4.8</v>
+        <v>25.5</v>
       </c>
       <c r="Q15">
-        <v>0.02116402116402116</v>
+        <v>0.03692976104272266</v>
       </c>
       <c r="R15">
-        <v>0.3555555555555556</v>
+        <v>0.2901023890784983</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>0.01200000000000045</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>0.0004703668861712313</v>
       </c>
       <c r="U15">
-        <v>21.6</v>
+        <v>122.7</v>
       </c>
       <c r="V15">
-        <v>0.09523809523809523</v>
+        <v>0.177697320782042</v>
       </c>
       <c r="W15">
-        <v>0.213946117274168</v>
+        <v>0.2345250800426894</v>
       </c>
       <c r="X15">
-        <v>0.06690267240641959</v>
+        <v>0.1368681356074014</v>
       </c>
       <c r="Y15">
-        <v>0.1470434448677484</v>
+        <v>0.09765694443528802</v>
       </c>
       <c r="Z15">
-        <v>0.567098508922024</v>
+        <v>0.2616350466339517</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>3.681802294490827e-05</v>
       </c>
       <c r="AB15">
-        <v>0.05911440053284901</v>
+        <v>0.1026996746644975</v>
       </c>
       <c r="AC15">
-        <v>-0.05911440053284901</v>
+        <v>-0.1026628566415526</v>
       </c>
       <c r="AD15">
-        <v>144.3</v>
+        <v>804.9</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.766353297102702</v>
       </c>
       <c r="AF15">
-        <v>144.3</v>
+        <v>806.6663532971027</v>
       </c>
       <c r="AG15">
-        <v>122.7</v>
+        <v>683.9663532971026</v>
       </c>
       <c r="AH15">
-        <v>0.3888439773645918</v>
+        <v>0.5387954060820556</v>
       </c>
       <c r="AI15">
-        <v>0.6668207024029575</v>
+        <v>0.5687291942747683</v>
       </c>
       <c r="AJ15">
-        <v>0.3510729613733906</v>
+        <v>0.4976232060220229</v>
       </c>
       <c r="AK15">
-        <v>0.6298767967145791</v>
+        <v>0.527887717047373</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-0.338</v>
+        <v>-0.552</v>
+      </c>
+      <c r="AN15">
+        <v>2017.293233082707</v>
+      </c>
+      <c r="AP15">
+        <v>1714.20138670953</v>
       </c>
       <c r="AQ15">
         <v>-0</v>
@@ -2311,7 +2263,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bao Viet Securities Joint Stock Company (HNX:BVS)</t>
+          <t>BIDV Securities Joint Stock Company (HOSE:BSI)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2320,10 +2272,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.274</v>
+        <v>0.184</v>
       </c>
       <c r="E16">
-        <v>0.189</v>
+        <v>-0.0237</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2332,103 +2284,94 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0.003263249173825468</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>0.002673253723197823</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>10.2</v>
+        <v>7.17</v>
       </c>
       <c r="L16">
-        <v>0.253731343283582</v>
+        <v>0.1633257403189066</v>
       </c>
       <c r="M16">
-        <v>3.14</v>
+        <v>-0</v>
       </c>
       <c r="N16">
-        <v>0.02464678178963893</v>
+        <v>-0</v>
       </c>
       <c r="O16">
-        <v>0.307843137254902</v>
+        <v>-0</v>
       </c>
       <c r="P16">
-        <v>3.14</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.02464678178963893</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>0.307843137254902</v>
+        <v>-0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
       <c r="U16">
-        <v>3.23</v>
+        <v>123.1</v>
       </c>
       <c r="V16">
-        <v>0.02535321821036107</v>
+        <v>1.386261261261261</v>
       </c>
       <c r="W16">
-        <v>0.1259259259259259</v>
+        <v>0.09944521497919556</v>
       </c>
       <c r="X16">
-        <v>0.07150541882546133</v>
+        <v>0.1392706261970852</v>
       </c>
       <c r="Y16">
-        <v>0.05442050710046459</v>
+        <v>-0.0398254112178896</v>
       </c>
       <c r="Z16">
-        <v>0.3934422882656819</v>
+        <v>0.2253593429158111</v>
       </c>
       <c r="AA16">
-        <v>0.001051771061969705</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.0605287198393141</v>
+        <v>0.103000362013656</v>
       </c>
       <c r="AC16">
-        <v>-0.05947694877734439</v>
+        <v>-0.103000362013656</v>
       </c>
       <c r="AD16">
-        <v>101.9</v>
+        <v>109</v>
       </c>
       <c r="AE16">
-        <v>0.509086916061081</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>102.4090869160611</v>
+        <v>109</v>
       </c>
       <c r="AG16">
-        <v>99.17908691606108</v>
+        <v>-14.09999999999999</v>
       </c>
       <c r="AH16">
-        <v>0.445626795225319</v>
+        <v>0.551061678463094</v>
       </c>
       <c r="AI16">
-        <v>0.5265002707058871</v>
+        <v>0.3741846893237212</v>
       </c>
       <c r="AJ16">
-        <v>0.4377239235358166</v>
+        <v>-0.1887550200803212</v>
       </c>
       <c r="AK16">
-        <v>0.5185046024377133</v>
+        <v>-0.0838287752675386</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-0.662</v>
-      </c>
-      <c r="AN16">
-        <v>437.3390557939914</v>
-      </c>
-      <c r="AP16">
-        <v>425.6613172363136</v>
+        <v>-0.351</v>
       </c>
       <c r="AQ16">
         <v>-0</v>
@@ -2442,7 +2385,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SSI Securities Corporation (HOSE:SSI)</t>
+          <t>MB Securities Joint Stock Company (HNX:MBS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2451,10 +2394,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.216</v>
+        <v>0.289</v>
       </c>
       <c r="E17">
-        <v>0.136</v>
+        <v>0.9940000000000001</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2463,228 +2406,97 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>-0.0001700041870871956</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>-0.0001364822347038049</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>91.2</v>
+        <v>25.7</v>
       </c>
       <c r="L17">
-        <v>0.4022937803264226</v>
+        <v>0.3458950201884253</v>
       </c>
       <c r="M17">
-        <v>29.202</v>
+        <v>0.013</v>
       </c>
       <c r="N17">
-        <v>0.01306109669916808</v>
+        <v>6.612410986775178e-05</v>
       </c>
       <c r="O17">
-        <v>0.3201973684210526</v>
+        <v>0.0005058365758754864</v>
       </c>
       <c r="P17">
-        <v>28.5</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.01274711512657662</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>0.3125</v>
+        <v>-0</v>
       </c>
       <c r="S17">
-        <v>0.7019999999999982</v>
+        <v>0.013</v>
       </c>
       <c r="T17">
-        <v>0.02403944935278399</v>
+        <v>1</v>
       </c>
       <c r="U17">
-        <v>12.7</v>
+        <v>26.8</v>
       </c>
       <c r="V17">
-        <v>0.005680293407281509</v>
+        <v>0.1363173957273652</v>
       </c>
       <c r="W17">
-        <v>0.2241336937822561</v>
+        <v>0.1807313642756681</v>
       </c>
       <c r="X17">
-        <v>0.06809146453159266</v>
+        <v>0.1534783973810027</v>
       </c>
       <c r="Y17">
-        <v>0.1560422292506635</v>
+        <v>0.02725296689466533</v>
       </c>
       <c r="Z17">
-        <v>0.2014694383225447</v>
+        <v>0.1713244788784357</v>
       </c>
       <c r="AA17">
-        <v>-2.74969991667813e-05</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.05950672590825345</v>
+        <v>0.1044960213904922</v>
       </c>
       <c r="AC17">
-        <v>-0.05953422290742023</v>
+        <v>-0.1044960213904922</v>
       </c>
       <c r="AD17">
-        <v>1500.9</v>
+        <v>310.2</v>
       </c>
       <c r="AE17">
-        <v>18.39269974606334</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1519.292699746063</v>
+        <v>310.2</v>
       </c>
       <c r="AG17">
-        <v>1506.592699746063</v>
+        <v>283.4</v>
       </c>
       <c r="AH17">
-        <v>0.4045952580208751</v>
+        <v>0.6120757695343331</v>
       </c>
       <c r="AI17">
-        <v>0.7414465436016359</v>
+        <v>0.659719268396427</v>
       </c>
       <c r="AJ17">
-        <v>0.4025747217410647</v>
+        <v>0.5904166666666666</v>
       </c>
       <c r="AK17">
-        <v>0.7398340702821878</v>
+        <v>0.6391520072169599</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1.33</v>
-      </c>
-      <c r="AN17">
-        <v>412.3351648351648</v>
-      </c>
-      <c r="AP17">
-        <v>413.8990933368306</v>
-      </c>
-      <c r="AQ17">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Petrovietnam Securities Incorporated (HNX:PSI)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>0.204</v>
-      </c>
-      <c r="E18">
-        <v>0.285</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>1.45</v>
-      </c>
-      <c r="L18">
-        <v>0.1306306306306306</v>
-      </c>
-      <c r="M18">
-        <v>-0</v>
-      </c>
-      <c r="N18">
-        <v>-0</v>
-      </c>
-      <c r="O18">
-        <v>-0</v>
-      </c>
-      <c r="P18">
-        <v>-0</v>
-      </c>
-      <c r="Q18">
-        <v>-0</v>
-      </c>
-      <c r="R18">
-        <v>-0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="V18">
-        <v>0.01311068702290076</v>
-      </c>
-      <c r="W18">
-        <v>0.05390334572490706</v>
-      </c>
-      <c r="X18">
-        <v>0.0726473709791174</v>
-      </c>
-      <c r="Y18">
-        <v>-0.01874402525421034</v>
-      </c>
-      <c r="Z18">
-        <v>0.2480114398069533</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0.06083984207145136</v>
-      </c>
-      <c r="AC18">
-        <v>-0.06083984207145136</v>
-      </c>
-      <c r="AD18">
-        <v>44.3</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>44.3</v>
-      </c>
-      <c r="AG18">
-        <v>43.613</v>
-      </c>
-      <c r="AH18">
-        <v>0.4581178903826267</v>
-      </c>
-      <c r="AI18">
-        <v>0.6135734072022161</v>
-      </c>
-      <c r="AJ18">
-        <v>0.4542405715892639</v>
-      </c>
-      <c r="AK18">
-        <v>0.609861144127641</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>-0.073</v>
-      </c>
-      <c r="AQ18">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/vietnam/vietnam_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ17"/>
+  <dimension ref="A1:AQ21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.23</v>
+        <v>0.0861</v>
       </c>
       <c r="E2">
-        <v>0.151</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="G2">
-        <v>0.01016677897574124</v>
+        <v>0.01178372749445068</v>
       </c>
       <c r="H2">
-        <v>0.01016677897574124</v>
+        <v>0.01178372749445068</v>
       </c>
       <c r="I2">
-        <v>0.005366794024365974</v>
+        <v>0.003274827871380888</v>
       </c>
       <c r="J2">
-        <v>0.004466755280478317</v>
+        <v>0.002829610669569921</v>
       </c>
       <c r="K2">
-        <v>395.02</v>
+        <v>281.591</v>
       </c>
       <c r="L2">
-        <v>0.3327324797843665</v>
+        <v>0.2572241557278964</v>
       </c>
       <c r="M2">
-        <v>103.258</v>
+        <v>127.9112</v>
       </c>
       <c r="N2">
-        <v>0.0273505767677169</v>
+        <v>0.01649594408119575</v>
       </c>
       <c r="O2">
-        <v>0.2613994228140347</v>
+        <v>0.4542446313980206</v>
       </c>
       <c r="P2">
-        <v>103.148</v>
+        <v>127.9032</v>
       </c>
       <c r="Q2">
-        <v>0.02732144039625465</v>
+        <v>0.0164949123689403</v>
       </c>
       <c r="R2">
-        <v>0.2611209559009671</v>
+        <v>0.4542162213991214</v>
       </c>
       <c r="S2">
-        <v>0.1100000000000013</v>
+        <v>0.007999999999999119</v>
       </c>
       <c r="T2">
-        <v>0.00106529276181992</v>
+        <v>6.254338947644239e-05</v>
       </c>
       <c r="U2">
-        <v>812.603</v>
+        <v>655.787</v>
       </c>
       <c r="V2">
-        <v>0.2152391169030686</v>
+        <v>0.08457293560825886</v>
       </c>
       <c r="W2">
-        <v>0.1362068965517241</v>
+        <v>0.06618705035971223</v>
       </c>
       <c r="X2">
-        <v>0.1225031797533433</v>
+        <v>0.09095827623155181</v>
       </c>
       <c r="Y2">
-        <v>0.01370371679838085</v>
+        <v>-0.02477122587183958</v>
       </c>
       <c r="Z2">
-        <v>0.2007497777383962</v>
+        <v>0.1626582750773347</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1004920230939557</v>
+        <v>0.08174331981144894</v>
       </c>
       <c r="AC2">
-        <v>-0.1002276077603401</v>
+        <v>-0.07953831551895479</v>
       </c>
       <c r="AD2">
-        <v>3410.764</v>
+        <v>4219.5</v>
       </c>
       <c r="AE2">
-        <v>22.13771067136359</v>
+        <v>12.829738421816</v>
       </c>
       <c r="AF2">
-        <v>3432.901710671364</v>
+        <v>4232.329738421816</v>
       </c>
       <c r="AG2">
-        <v>2620.298710671364</v>
+        <v>3576.542738421816</v>
       </c>
       <c r="AH2">
-        <v>0.4762460924594473</v>
+        <v>0.3530934423997268</v>
       </c>
       <c r="AI2">
-        <v>0.4633482592604523</v>
+        <v>0.4828433818675309</v>
       </c>
       <c r="AJ2">
-        <v>0.4097002242007607</v>
+        <v>0.3156522380053414</v>
       </c>
       <c r="AK2">
-        <v>0.3972377276414568</v>
+        <v>0.4410234647547288</v>
       </c>
       <c r="AL2">
-        <v>20.69</v>
+        <v>20.702</v>
       </c>
       <c r="AM2">
-        <v>-63.77800000000001</v>
+        <v>-6.217999999999996</v>
       </c>
       <c r="AN2">
-        <v>176.0030961349915</v>
+        <v>284.2945694650317</v>
       </c>
       <c r="AO2">
-        <v>0.2319961333977767</v>
+        <v>0.1535600425079703</v>
       </c>
       <c r="AP2">
-        <v>135.2133087709048</v>
+        <v>240.9744467337162</v>
       </c>
       <c r="AQ2">
-        <v>-0.075261061808147</v>
+        <v>-0.5112576391122551</v>
       </c>
     </row>
     <row r="3">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.5156249999999999</v>
+        <v>0.535042735042735</v>
       </c>
       <c r="H3">
-        <v>0.5156249999999999</v>
+        <v>0.535042735042735</v>
       </c>
       <c r="I3">
-        <v>0.3734375</v>
+        <v>0.2188034188034188</v>
       </c>
       <c r="J3">
-        <v>0.3709593894009217</v>
+        <v>0.2188034188034188</v>
       </c>
       <c r="K3">
-        <v>19.8</v>
+        <v>-2.57</v>
       </c>
       <c r="L3">
-        <v>1.546875</v>
+        <v>-0.2196581196581197</v>
       </c>
       <c r="M3">
-        <v>0.178</v>
+        <v>0.147</v>
       </c>
       <c r="N3">
-        <v>0.00166510757717493</v>
+        <v>0.001054519368723099</v>
       </c>
       <c r="O3">
-        <v>0.008989898989898989</v>
+        <v>-0.05719844357976653</v>
       </c>
       <c r="P3">
-        <v>0.178</v>
+        <v>0.147</v>
       </c>
       <c r="Q3">
-        <v>0.00166510757717493</v>
+        <v>0.001054519368723099</v>
       </c>
       <c r="R3">
-        <v>0.008989898989898989</v>
+        <v>-0.05719844357976653</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,58 +764,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="V3">
-        <v>0.0205799812909261</v>
+        <v>0.01291248206599713</v>
       </c>
       <c r="X3">
-        <v>0.1624429513259506</v>
+        <v>0.1130773901976515</v>
       </c>
       <c r="AB3">
-        <v>0.1072009147679779</v>
+        <v>0.08602839235570586</v>
       </c>
       <c r="AD3">
-        <v>192.3</v>
+        <v>197.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>192.3</v>
+        <v>197.2</v>
       </c>
       <c r="AG3">
-        <v>190.1</v>
+        <v>195.4</v>
       </c>
       <c r="AH3">
-        <v>0.6427139037433155</v>
+        <v>0.5858585858585857</v>
       </c>
       <c r="AI3">
-        <v>0.534018328242155</v>
+        <v>0.5452032070776887</v>
       </c>
       <c r="AJ3">
-        <v>0.6400673400673401</v>
+        <v>0.5836320191158901</v>
       </c>
       <c r="AK3">
-        <v>0.5311539536183292</v>
+        <v>0.5429285912753542</v>
       </c>
       <c r="AL3">
         <v>18.1</v>
       </c>
       <c r="AM3">
-        <v>-49.2</v>
+        <v>5.400000000000002</v>
       </c>
       <c r="AN3">
-        <v>27.12270803949225</v>
+        <v>37.85028790786948</v>
       </c>
       <c r="AO3">
-        <v>0.2640883977900552</v>
+        <v>0.1414364640883978</v>
       </c>
       <c r="AP3">
-        <v>26.81241184767278</v>
+        <v>37.50479846449136</v>
       </c>
       <c r="AQ3">
-        <v>-0.09715447154471546</v>
+        <v>0.4740740740740739</v>
       </c>
     </row>
     <row r="4">
@@ -834,8 +834,23 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.671</v>
+      </c>
+      <c r="L4">
+        <v>0.438562091503268</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -843,41 +858,47 @@
       <c r="N4">
         <v>-0</v>
       </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
       <c r="P4">
         <v>-0</v>
       </c>
       <c r="Q4">
         <v>-0</v>
       </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>14.4</v>
+        <v>1.57</v>
       </c>
       <c r="V4">
-        <v>1.959183673469388</v>
+        <v>0.1427272727272727</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>0.03994047619047619</v>
       </c>
       <c r="X4">
-        <v>0.08949199776307479</v>
+        <v>0.07364408464649556</v>
       </c>
       <c r="Y4">
-        <v>-0.08949199776307479</v>
+        <v>-0.03370360845601937</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>0.6375</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08949199776307479</v>
+        <v>0.07364408464649556</v>
       </c>
       <c r="AC4">
-        <v>-0.08949199776307479</v>
+        <v>-0.07364408464649556</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -889,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-14.4</v>
+        <v>-1.57</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -898,16 +919,19 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>2.042553191489362</v>
+        <v>-0.1664899257688229</v>
       </c>
       <c r="AK4">
-        <v>-5.999999999999999</v>
+        <v>-0.1010946555054733</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-0.092</v>
+      </c>
+      <c r="AQ4">
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -918,7 +942,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Asia Pacific Securities Joint Stock Company (HNX:APS)</t>
+          <t>VIX Securities Joint Stock Company (HOSE:VIX)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -926,23 +950,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
       <c r="K5">
-        <v>5.53</v>
-      </c>
-      <c r="L5">
-        <v>0.1498644986449865</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -950,80 +959,71 @@
       <c r="N5">
         <v>-0</v>
       </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
       <c r="P5">
         <v>-0</v>
       </c>
       <c r="Q5">
         <v>-0</v>
       </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>8.289999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="V5">
-        <v>0.2800675675675675</v>
+        <v>0.1945450671212444</v>
       </c>
       <c r="W5">
-        <v>0.1362068965517241</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>0.08975778823783252</v>
+        <v>0.07364408464649556</v>
       </c>
       <c r="Y5">
-        <v>0.04644910831389161</v>
+        <v>-0.07364408464649556</v>
       </c>
       <c r="Z5">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08973027086007183</v>
+        <v>0.07364408464649556</v>
       </c>
       <c r="AC5">
-        <v>-0.08973027086007183</v>
+        <v>-0.07364408464649556</v>
       </c>
       <c r="AD5">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-8.095999999999998</v>
+        <v>-91.3</v>
       </c>
       <c r="AH5">
-        <v>0.006511378129824797</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.004136989806798311</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.3764880952380951</v>
+        <v>-0.2415343915343915</v>
       </c>
       <c r="AK5">
-        <v>-0.2097192000828929</v>
+        <v>-0.3453101361573374</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AQ5">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Agribank Securities Corporation (HOSE:AGR)</t>
+          <t>SaiGon - Hanoi Securities Joint Stock Company (HNX:SHS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.164</v>
+        <v>0.129</v>
       </c>
       <c r="E6">
-        <v>0.143</v>
+        <v>0.0605</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>7.34</v>
+        <v>21.5</v>
       </c>
       <c r="L6">
-        <v>0.4421686746987951</v>
+        <v>0.2621951219512195</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1088,61 +1088,61 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.623</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V6">
-        <v>0.009188790560471977</v>
+        <v>0.1053800983970798</v>
       </c>
       <c r="W6">
-        <v>0.07153996101364522</v>
+        <v>0.0542929292929293</v>
       </c>
       <c r="X6">
-        <v>0.09122060984018729</v>
+        <v>0.07436518742984788</v>
       </c>
       <c r="Y6">
-        <v>-0.01968064882654207</v>
+        <v>-0.02007225813691858</v>
       </c>
       <c r="Z6">
-        <v>0.159186804756425</v>
+        <v>0.1872530885341737</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.09049417010580531</v>
+        <v>0.07417713126411121</v>
       </c>
       <c r="AC6">
-        <v>-0.09049417010580531</v>
+        <v>-0.07417713126411121</v>
       </c>
       <c r="AD6">
-        <v>2.89</v>
+        <v>16.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.89</v>
+        <v>16.3</v>
       </c>
       <c r="AG6">
-        <v>2.267</v>
+        <v>-50.10000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.04088272740132975</v>
+        <v>0.02521658415841584</v>
       </c>
       <c r="AI6">
-        <v>0.02683628934905748</v>
+        <v>0.03767044141437486</v>
       </c>
       <c r="AJ6">
-        <v>0.03235474617152155</v>
+        <v>-0.0863793103448276</v>
       </c>
       <c r="AK6">
-        <v>0.02117365761625898</v>
+        <v>-0.1367731367731368</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-0.055</v>
+        <v>-0.205</v>
       </c>
       <c r="AQ6">
         <v>-0</v>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VIX Securities Joint Stock Company (HOSE:VIX)</t>
+          <t>Agribank Securities Corporation (HOSE:AGR)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1164,80 +1164,113 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.156</v>
+      </c>
+      <c r="E7">
+        <v>0.314</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
       <c r="K7">
-        <v>0</v>
+        <v>6.45</v>
+      </c>
+      <c r="L7">
+        <v>0.4358108108108108</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>5.385000000000001</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.0380028228652082</v>
+      </c>
+      <c r="O7">
+        <v>0.8348837209302327</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>5.385000000000001</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.0380028228652082</v>
+      </c>
+      <c r="R7">
+        <v>0.8348837209302327</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>84.90000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="V7">
-        <v>0.5342983008181246</v>
+        <v>0.06951305575158787</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>0.06154580152671756</v>
       </c>
       <c r="X7">
-        <v>0.09163069601986303</v>
+        <v>0.07761783487858709</v>
       </c>
       <c r="Y7">
-        <v>-0.09163069601986303</v>
+        <v>-0.01607203335186953</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>0.1382312010236581</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.09072000959406794</v>
+        <v>0.07628152991463456</v>
       </c>
       <c r="AC7">
-        <v>-0.09072000959406794</v>
+        <v>-0.07628152991463456</v>
       </c>
       <c r="AD7">
-        <v>8.380000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>8.380000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="AG7">
-        <v>-76.52000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="AH7">
-        <v>0.05009564801530369</v>
+        <v>0.1247683755404571</v>
       </c>
       <c r="AI7">
-        <v>0.0244900344847741</v>
+        <v>0.1665292662819456</v>
       </c>
       <c r="AJ7">
-        <v>-0.9288662296673952</v>
+        <v>0.06806971390989806</v>
       </c>
       <c r="AK7">
-        <v>-0.2974191542288558</v>
+        <v>0.09286675639300135</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>-0.042</v>
+      </c>
+      <c r="AQ7">
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -1248,7 +1281,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Saigon - Hanoi Securities Joint Stock Company (HNX:SHS)</t>
+          <t>Everest Securities Joint Stock Company (HNX:EVS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1256,104 +1289,74 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.189</v>
-      </c>
-      <c r="E8">
-        <v>0.151</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
       <c r="K8">
-        <v>24.7</v>
-      </c>
-      <c r="L8">
-        <v>0.3130544993662864</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>10.4</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.0362495643081213</v>
-      </c>
-      <c r="O8">
-        <v>0.4210526315789474</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>10.4</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.0362495643081213</v>
-      </c>
-      <c r="R8">
-        <v>0.4210526315789474</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>22.6</v>
+        <v>1.83</v>
       </c>
       <c r="V8">
-        <v>0.07877309166957129</v>
+        <v>0.03221830985915494</v>
       </c>
       <c r="W8">
-        <v>0.1374513077351141</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>0.09876462251945736</v>
+        <v>0.07928784483571667</v>
       </c>
       <c r="Y8">
-        <v>0.03868668521565671</v>
+        <v>-0.07928784483571667</v>
       </c>
       <c r="Z8">
-        <v>0.2509541984732825</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0940539136154785</v>
+        <v>0.07720331479920317</v>
       </c>
       <c r="AC8">
-        <v>-0.0940539136154785</v>
+        <v>-0.07720331479920317</v>
       </c>
       <c r="AD8">
-        <v>65.59999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>65.59999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AG8">
-        <v>42.99999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="AH8">
-        <v>0.1860992907801418</v>
+        <v>0.1683748169838946</v>
       </c>
       <c r="AI8">
-        <v>0.1421143847487002</v>
+        <v>0.1251360174102285</v>
       </c>
       <c r="AJ8">
-        <v>0.1303425280387996</v>
+        <v>0.1454791635324206</v>
       </c>
       <c r="AK8">
-        <v>0.09794988610478358</v>
+        <v>0.1073609414899522</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1370,7 +1373,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SSI Securities Corporation (HOSE:SSI)</t>
+          <t>FPT Securities Joint Stock Company (HOSE:FTS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1379,10 +1382,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.235</v>
+        <v>0.185</v>
       </c>
       <c r="E9">
-        <v>0.218</v>
+        <v>0.162</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1391,103 +1394,97 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.003641763879307881</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0.002915107577303125</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>103.2</v>
+        <v>20.3</v>
       </c>
       <c r="L9">
-        <v>0.3975346687211094</v>
+        <v>0.5</v>
       </c>
       <c r="M9">
-        <v>41.685</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>0.03765582655826558</v>
+        <v>0.01018329938900204</v>
       </c>
       <c r="O9">
-        <v>0.4039244186046512</v>
+        <v>0.1970443349753694</v>
       </c>
       <c r="P9">
-        <v>41.6</v>
+        <v>4</v>
       </c>
       <c r="Q9">
-        <v>0.03757904245709124</v>
+        <v>0.01018329938900204</v>
       </c>
       <c r="R9">
-        <v>0.4031007751937984</v>
+        <v>0.1970443349753694</v>
       </c>
       <c r="S9">
-        <v>0.08500000000000085</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.002039102794770321</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>25.8</v>
+        <v>32.7</v>
       </c>
       <c r="V9">
-        <v>0.02330623306233062</v>
+        <v>0.08324847250509165</v>
       </c>
       <c r="W9">
-        <v>0.1957882754695504</v>
+        <v>0.1487179487179487</v>
       </c>
       <c r="X9">
-        <v>0.1230145834806527</v>
+        <v>0.08054193602661647</v>
       </c>
       <c r="Y9">
-        <v>0.07277369198889766</v>
+        <v>0.06817601269133225</v>
       </c>
       <c r="Z9">
-        <v>0.1276759201616704</v>
+        <v>0.2614294913071474</v>
       </c>
       <c r="AA9">
-        <v>0.0003721890423024342</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.1005853157144395</v>
+        <v>0.07783731885565068</v>
       </c>
       <c r="AC9">
-        <v>-0.1002131266721371</v>
+        <v>-0.07783731885565068</v>
       </c>
       <c r="AD9">
-        <v>897.1</v>
+        <v>97.2</v>
       </c>
       <c r="AE9">
-        <v>17.97299048465837</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>915.0729904846584</v>
+        <v>97.2</v>
       </c>
       <c r="AG9">
-        <v>889.2729904846584</v>
+        <v>64.5</v>
       </c>
       <c r="AH9">
-        <v>0.452542017420118</v>
+        <v>0.1983673469387755</v>
       </c>
       <c r="AI9">
-        <v>0.4962776694527823</v>
+        <v>0.3959266802443992</v>
       </c>
       <c r="AJ9">
-        <v>0.4454666244163126</v>
+        <v>0.1410452656899191</v>
       </c>
       <c r="AK9">
-        <v>0.4891294217222806</v>
+        <v>0.3031015037593985</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-3.88</v>
-      </c>
-      <c r="AN9">
-        <v>197.5991189427313</v>
-      </c>
-      <c r="AP9">
-        <v>195.8751080362684</v>
+        <v>-0.056</v>
       </c>
       <c r="AQ9">
         <v>-0</v>
@@ -1501,7 +1498,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bao Viet Securities Joint Stock Company (HNX:BVS)</t>
+          <t>Ho Chi Minh City Securities Corporation (HOSE:HCM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1510,10 +1507,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.153</v>
+        <v>-0.0024</v>
       </c>
       <c r="E10">
-        <v>0.104</v>
+        <v>-0.0471</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1522,34 +1519,34 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.01107062157700745</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>0.00884957812312033</v>
       </c>
       <c r="K10">
-        <v>8.380000000000001</v>
+        <v>25.5</v>
       </c>
       <c r="L10">
-        <v>0.236056338028169</v>
+        <v>0.2670157068062827</v>
       </c>
       <c r="M10">
-        <v>2.38</v>
+        <v>18.8</v>
       </c>
       <c r="N10">
-        <v>0.03808</v>
+        <v>0.02932459834659179</v>
       </c>
       <c r="O10">
-        <v>0.2840095465393794</v>
+        <v>0.7372549019607844</v>
       </c>
       <c r="P10">
-        <v>2.38</v>
+        <v>18.8</v>
       </c>
       <c r="Q10">
-        <v>0.03808</v>
+        <v>0.02932459834659179</v>
       </c>
       <c r="R10">
-        <v>0.2840095465393794</v>
+        <v>0.7372549019607844</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1558,61 +1555,67 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>7.17</v>
+        <v>103.6</v>
       </c>
       <c r="V10">
-        <v>0.11472</v>
+        <v>0.1615972547184527</v>
       </c>
       <c r="W10">
-        <v>0.09098805646036918</v>
+        <v>0.07609668755595345</v>
       </c>
       <c r="X10">
-        <v>0.1210913614886651</v>
+        <v>0.08807364581149491</v>
       </c>
       <c r="Y10">
-        <v>-0.03010330502829588</v>
+        <v>-0.01197695825554146</v>
       </c>
       <c r="Z10">
-        <v>0.1860879593227447</v>
+        <v>0.1824734610580112</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>0.001614813149029025</v>
       </c>
       <c r="AB10">
-        <v>0.1002276077603401</v>
+        <v>0.08085419838996694</v>
       </c>
       <c r="AC10">
-        <v>-0.1002276077603401</v>
+        <v>-0.0792393852409379</v>
       </c>
       <c r="AD10">
-        <v>48.7</v>
+        <v>328.6</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>3.263778196978942</v>
       </c>
       <c r="AF10">
-        <v>48.7</v>
+        <v>331.863778196979</v>
       </c>
       <c r="AG10">
-        <v>41.53</v>
+        <v>228.263778196979</v>
       </c>
       <c r="AH10">
-        <v>0.4379496402877698</v>
+        <v>0.3410854398012259</v>
       </c>
       <c r="AI10">
-        <v>0.3451452870304748</v>
+        <v>0.497723165308086</v>
       </c>
       <c r="AJ10">
-        <v>0.3992117658367779</v>
+        <v>0.2625641692484447</v>
       </c>
       <c r="AK10">
-        <v>0.3100873590681699</v>
+        <v>0.4053239697478176</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1.95</v>
+        <v>-0.08699999999999999</v>
+      </c>
+      <c r="AN10">
+        <v>192.1637426900585</v>
+      </c>
+      <c r="AP10">
+        <v>133.4875895888766</v>
       </c>
       <c r="AQ10">
         <v>-0</v>
@@ -1635,28 +1638,25 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.00323</v>
-      </c>
-      <c r="E11">
-        <v>-0.0781</v>
+        <v>0.0118</v>
       </c>
       <c r="G11">
-        <v>0.07391891891891891</v>
+        <v>0.09721815519765739</v>
       </c>
       <c r="H11">
-        <v>0.07391891891891891</v>
+        <v>0.09721815519765739</v>
       </c>
       <c r="I11">
-        <v>0.0002702702702702703</v>
+        <v>0.009062957540263544</v>
       </c>
       <c r="J11">
-        <v>0.0001871747523921437</v>
+        <v>0.009062957540263544</v>
       </c>
       <c r="K11">
-        <v>2.91</v>
+        <v>-6.25</v>
       </c>
       <c r="L11">
-        <v>0.03932432432432433</v>
+        <v>-0.09150805270863836</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1665,7 +1665,7 @@
         <v>-0</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1674,79 +1674,79 @@
         <v>-0</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>9.32</v>
+        <v>1.85</v>
       </c>
       <c r="V11">
-        <v>0.1838264299802761</v>
+        <v>0.02955271565495208</v>
       </c>
       <c r="W11">
-        <v>0.02080057183702645</v>
+        <v>-0.03850893407270486</v>
       </c>
       <c r="X11">
-        <v>0.1221268460271134</v>
+        <v>0.09604226301989782</v>
       </c>
       <c r="Y11">
-        <v>-0.101326274190087</v>
+        <v>-0.1345511970926027</v>
       </c>
       <c r="Z11">
-        <v>0.556558363417569</v>
+        <v>0.4044291804831833</v>
       </c>
       <c r="AA11">
-        <v>0.0001041736738644602</v>
+        <v>0.003665324490762671</v>
       </c>
       <c r="AB11">
-        <v>0.1004225378452536</v>
+        <v>0.08306196087195516</v>
       </c>
       <c r="AC11">
-        <v>-0.1003183641713892</v>
+        <v>-0.07939663638119249</v>
       </c>
       <c r="AD11">
-        <v>40.8</v>
+        <v>50.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>40.8</v>
+        <v>50.3</v>
       </c>
       <c r="AG11">
-        <v>31.48</v>
+        <v>48.45</v>
       </c>
       <c r="AH11">
-        <v>0.4459016393442622</v>
+        <v>0.445527015057573</v>
       </c>
       <c r="AI11">
-        <v>0.1403991741225051</v>
+        <v>0.1755059316120028</v>
       </c>
       <c r="AJ11">
-        <v>0.383061572158676</v>
+        <v>0.4362899594777127</v>
       </c>
       <c r="AK11">
-        <v>0.1119169510807736</v>
+        <v>0.1701492537313433</v>
       </c>
       <c r="AL11">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AM11">
-        <v>-7.380000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="AN11">
-        <v>6.486486486486486</v>
+        <v>7.552552552552552</v>
       </c>
       <c r="AO11">
-        <v>0.007722007722007722</v>
+        <v>0.239922480620155</v>
       </c>
       <c r="AP11">
-        <v>5.00476947535771</v>
+        <v>7.274774774774774</v>
       </c>
       <c r="AQ11">
-        <v>-0.002710027100271002</v>
+        <v>1.5475</v>
       </c>
     </row>
     <row r="12">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viet Capital Securities Joint Stock Company (HOSE:VCI)</t>
+          <t>BIDV Securities Joint Stock Company (HOSE:BSI)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.23</v>
+        <v>0.053</v>
       </c>
       <c r="E12">
-        <v>0.176</v>
+        <v>0.09539999999999998</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1784,91 +1784,91 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>54.8</v>
+        <v>14.8</v>
       </c>
       <c r="L12">
-        <v>0.4349206349206349</v>
+        <v>0.3252747252747253</v>
       </c>
       <c r="M12">
-        <v>16.7</v>
+        <v>9.267999999999999</v>
       </c>
       <c r="N12">
-        <v>0.03926640018810251</v>
+        <v>0.02352881441990353</v>
       </c>
       <c r="O12">
-        <v>0.3047445255474452</v>
+        <v>0.6262162162162161</v>
       </c>
       <c r="P12">
-        <v>16.7</v>
+        <v>9.26</v>
       </c>
       <c r="Q12">
-        <v>0.03926640018810251</v>
+        <v>0.02350850469662351</v>
       </c>
       <c r="R12">
-        <v>0.3047445255474452</v>
+        <v>0.6256756756756756</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>0.007999999999999119</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>0.0008631851532152697</v>
       </c>
       <c r="U12">
-        <v>77.09999999999999</v>
+        <v>59</v>
       </c>
       <c r="V12">
-        <v>0.1812837996708206</v>
+        <v>0.1497842091901498</v>
       </c>
       <c r="W12">
-        <v>0.1971223021582734</v>
+        <v>0.08087431693989071</v>
       </c>
       <c r="X12">
-        <v>0.1225031797533433</v>
+        <v>0.08442195535817115</v>
       </c>
       <c r="Y12">
-        <v>0.07461912240493009</v>
+        <v>-0.003547638418280444</v>
       </c>
       <c r="Z12">
-        <v>0.2390438247011953</v>
+        <v>0.2407407407407407</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.1004920230939557</v>
+        <v>0.07953831551895479</v>
       </c>
       <c r="AC12">
-        <v>-0.1004920230939557</v>
+        <v>-0.07953831551895479</v>
       </c>
       <c r="AD12">
-        <v>346.2</v>
+        <v>152.3</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>346.2</v>
+        <v>152.3</v>
       </c>
       <c r="AG12">
-        <v>269.1</v>
+        <v>93.30000000000001</v>
       </c>
       <c r="AH12">
-        <v>0.4487362281270252</v>
+        <v>0.2788355913584767</v>
       </c>
       <c r="AI12">
-        <v>0.5562339331619537</v>
+        <v>0.4458430913348946</v>
       </c>
       <c r="AJ12">
-        <v>0.3875288018433179</v>
+        <v>0.1915024630541872</v>
       </c>
       <c r="AK12">
-        <v>0.4934898221162664</v>
+        <v>0.3301486199575372</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-0.217</v>
+        <v>-0.44</v>
       </c>
       <c r="AQ12">
         <v>-0</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City Securities Corporation (HOSE:HCM)</t>
+          <t>Viet Capital Securities Joint Stock Company (HOSE:VCI)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.279</v>
+        <v>0.0262</v>
       </c>
       <c r="E13">
-        <v>0.165</v>
+        <v>-0.145</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1903,34 +1903,34 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.004419852414923821</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0.003539432014200039</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>39.8</v>
+        <v>16.4</v>
       </c>
       <c r="L13">
-        <v>0.3031226199543031</v>
+        <v>0.2081218274111675</v>
       </c>
       <c r="M13">
-        <v>6.39</v>
+        <v>21.5</v>
       </c>
       <c r="N13">
-        <v>0.01663629263212705</v>
+        <v>0.02803860198226396</v>
       </c>
       <c r="O13">
-        <v>0.1605527638190955</v>
+        <v>1.310975609756098</v>
       </c>
       <c r="P13">
-        <v>6.39</v>
+        <v>21.5</v>
       </c>
       <c r="Q13">
-        <v>0.01663629263212705</v>
+        <v>0.02803860198226396</v>
       </c>
       <c r="R13">
-        <v>0.1605527638190955</v>
+        <v>1.310975609756098</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1939,67 +1939,61 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>277.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="V13">
-        <v>0.7216870606612861</v>
+        <v>0.09533124673969744</v>
       </c>
       <c r="W13">
-        <v>0.1770462633451957</v>
+        <v>0.05937726285300507</v>
       </c>
       <c r="X13">
-        <v>0.138544680658354</v>
+        <v>0.08688011095822122</v>
       </c>
       <c r="Y13">
-        <v>0.03850158268684173</v>
+        <v>-0.02750284810521615</v>
       </c>
       <c r="Z13">
-        <v>0.2059936247416543</v>
+        <v>0.1445076104896387</v>
       </c>
       <c r="AA13">
-        <v>0.0007291004301317205</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.1029112051427342</v>
+        <v>0.08044982553116514</v>
       </c>
       <c r="AC13">
-        <v>-0.1021821047126025</v>
+        <v>-0.08044982553116514</v>
       </c>
       <c r="AD13">
-        <v>462.2</v>
+        <v>364.1</v>
       </c>
       <c r="AE13">
-        <v>2.398366889602511</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>464.5983668896025</v>
+        <v>364.1</v>
       </c>
       <c r="AG13">
-        <v>187.3983668896025</v>
+        <v>291</v>
       </c>
       <c r="AH13">
-        <v>0.5474246033868435</v>
+        <v>0.3219559642762402</v>
       </c>
       <c r="AI13">
-        <v>0.5809670072187852</v>
+        <v>0.5480957398765619</v>
       </c>
       <c r="AJ13">
-        <v>0.3279070908102921</v>
+        <v>0.2750992626205332</v>
       </c>
       <c r="AK13">
-        <v>0.3586582825228189</v>
+        <v>0.4922192151556157</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-0.123</v>
-      </c>
-      <c r="AN13">
-        <v>436.0377358490566</v>
-      </c>
-      <c r="AP13">
-        <v>176.7909121600024</v>
+        <v>-0.3</v>
       </c>
       <c r="AQ13">
         <v>-0</v>
@@ -2013,7 +2007,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Thien Viet Securities Joint Stock Company (HOSE:TVS)</t>
+          <t>Viet Dragon Securities Corporation (HOSE:VDS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2021,12 +2015,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.26</v>
-      </c>
-      <c r="E14">
-        <v>0.0668</v>
-      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2034,16 +2022,16 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>0.01526656042486041</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>0.0133113693529046</v>
       </c>
       <c r="K14">
-        <v>7.79</v>
+        <v>10.3</v>
       </c>
       <c r="L14">
-        <v>0.2128415300546448</v>
+        <v>0.4746543778801844</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2067,61 +2055,70 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>10.4</v>
+        <v>12.9</v>
       </c>
       <c r="V14">
-        <v>0.09252669039145907</v>
+        <v>0.08763586956521741</v>
       </c>
       <c r="W14">
-        <v>0.1106534090909091</v>
+        <v>0.1650641025641026</v>
       </c>
       <c r="X14">
-        <v>0.1336174876308616</v>
+        <v>0.09541095295170984</v>
       </c>
       <c r="Y14">
-        <v>-0.02296407853995248</v>
+        <v>0.06965314961239275</v>
       </c>
       <c r="Z14">
-        <v>0.1934665398033619</v>
+        <v>0.1424411862794786</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>0.001896087241632027</v>
       </c>
       <c r="AB14">
-        <v>0.102265674449063</v>
+        <v>0.08291290414455316</v>
       </c>
       <c r="AC14">
-        <v>-0.102265674449063</v>
+        <v>-0.08101681690292113</v>
       </c>
       <c r="AD14">
-        <v>122.3</v>
+        <v>111.2</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>3.743578193902646</v>
       </c>
       <c r="AF14">
-        <v>122.3</v>
+        <v>114.9435781939027</v>
       </c>
       <c r="AG14">
-        <v>111.9</v>
+        <v>102.0435781939026</v>
       </c>
       <c r="AH14">
-        <v>0.5210907541542394</v>
+        <v>0.4384756589722029</v>
       </c>
       <c r="AI14">
-        <v>0.6236613972463029</v>
+        <v>0.5454191258352102</v>
       </c>
       <c r="AJ14">
-        <v>0.4988854213107445</v>
+        <v>0.4094130686669744</v>
       </c>
       <c r="AK14">
-        <v>0.6025848142164781</v>
+        <v>0.5157790772156967</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>-1.77</v>
+      </c>
+      <c r="AN14">
+        <v>102.962962962963</v>
+      </c>
+      <c r="AP14">
+        <v>94.48479462398393</v>
+      </c>
+      <c r="AQ14">
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -2132,7 +2129,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VNDIRECT Securities Joint Stock Company (HOSE:VND)</t>
+          <t>SSI Securities Corporation (HOSE:SSI)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2141,10 +2138,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.476</v>
+        <v>0.0861</v>
       </c>
       <c r="E15">
-        <v>0.408</v>
+        <v>0.0688</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2153,103 +2150,97 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0.000175342563571548</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0.0001407228252429791</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>87.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="L15">
-        <v>0.3370398773006135</v>
+        <v>0.4058823529411765</v>
       </c>
       <c r="M15">
-        <v>25.512</v>
+        <v>61.6</v>
       </c>
       <c r="N15">
-        <v>0.03694713975380159</v>
+        <v>0.03055555555555555</v>
       </c>
       <c r="O15">
-        <v>0.2902389078498294</v>
+        <v>0.7439613526570049</v>
       </c>
       <c r="P15">
-        <v>25.5</v>
+        <v>61.6</v>
       </c>
       <c r="Q15">
-        <v>0.03692976104272266</v>
+        <v>0.03055555555555555</v>
       </c>
       <c r="R15">
-        <v>0.2901023890784983</v>
+        <v>0.7439613526570049</v>
       </c>
       <c r="S15">
-        <v>0.01200000000000045</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>0.0004703668861712313</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>122.7</v>
+        <v>16.9</v>
       </c>
       <c r="V15">
-        <v>0.177697320782042</v>
+        <v>0.008382936507936508</v>
       </c>
       <c r="W15">
-        <v>0.2345250800426894</v>
+        <v>0.08972691807542263</v>
       </c>
       <c r="X15">
-        <v>0.1368681356074014</v>
+        <v>0.09095827623155181</v>
       </c>
       <c r="Y15">
-        <v>0.09765694443528802</v>
+        <v>-0.001231358156129181</v>
       </c>
       <c r="Z15">
-        <v>0.2616350466339517</v>
+        <v>0.1137060364528176</v>
       </c>
       <c r="AA15">
-        <v>3.681802294490827e-05</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.1026996746644975</v>
+        <v>0.08174331981144894</v>
       </c>
       <c r="AC15">
-        <v>-0.1026628566415526</v>
+        <v>-0.08174331981144894</v>
       </c>
       <c r="AD15">
-        <v>804.9</v>
+        <v>1252.2</v>
       </c>
       <c r="AE15">
-        <v>1.766353297102702</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>806.6663532971027</v>
+        <v>1252.2</v>
       </c>
       <c r="AG15">
-        <v>683.9663532971026</v>
+        <v>1235.3</v>
       </c>
       <c r="AH15">
-        <v>0.5387954060820556</v>
+        <v>0.3831466862493116</v>
       </c>
       <c r="AI15">
-        <v>0.5687291942747683</v>
+        <v>0.5724866273487862</v>
       </c>
       <c r="AJ15">
-        <v>0.4976232060220229</v>
+        <v>0.3799403315596838</v>
       </c>
       <c r="AK15">
-        <v>0.527887717047373</v>
+        <v>0.5691577589384444</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-0.552</v>
-      </c>
-      <c r="AN15">
-        <v>2017.293233082707</v>
-      </c>
-      <c r="AP15">
-        <v>1714.20138670953</v>
+        <v>-6.39</v>
       </c>
       <c r="AQ15">
         <v>-0</v>
@@ -2263,7 +2254,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BIDV Securities Joint Stock Company (HOSE:BSI)</t>
+          <t>Thien Viet Securities Joint Stock Company (HOSE:TVS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2272,10 +2263,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.184</v>
+        <v>0.217</v>
       </c>
       <c r="E16">
-        <v>-0.0237</v>
+        <v>0.0755</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2284,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>0.002675039918430874</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>0.002146719534540776</v>
       </c>
       <c r="K16">
-        <v>7.17</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L16">
-        <v>0.1633257403189066</v>
+        <v>0.2176470588235294</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2317,64 +2308,73 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>123.1</v>
+        <v>6.98</v>
       </c>
       <c r="V16">
-        <v>1.386261261261261</v>
+        <v>0.0533231474407945</v>
       </c>
       <c r="W16">
-        <v>0.09944521497919556</v>
+        <v>0.1303523035230352</v>
       </c>
       <c r="X16">
-        <v>0.1392706261970852</v>
+        <v>0.09621236480932249</v>
       </c>
       <c r="Y16">
-        <v>-0.0398254112178896</v>
+        <v>0.03413993871371274</v>
       </c>
       <c r="Z16">
-        <v>0.2253593429158111</v>
+        <v>0.2376614762279694</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>0.0005101925336263803</v>
       </c>
       <c r="AB16">
-        <v>0.103000362013656</v>
+        <v>0.08310148502609932</v>
       </c>
       <c r="AC16">
-        <v>-0.103000362013656</v>
+        <v>-0.08259129249247293</v>
       </c>
       <c r="AD16">
-        <v>109</v>
+        <v>105.7</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>0.2788161780267767</v>
       </c>
       <c r="AF16">
-        <v>109</v>
+        <v>105.9788161780268</v>
       </c>
       <c r="AG16">
-        <v>-14.09999999999999</v>
+        <v>98.99881617802677</v>
       </c>
       <c r="AH16">
-        <v>0.551061678463094</v>
+        <v>0.447396765519033</v>
       </c>
       <c r="AI16">
-        <v>0.3741846893237212</v>
+        <v>0.5590224599699252</v>
       </c>
       <c r="AJ16">
-        <v>-0.1887550200803212</v>
+        <v>0.4306190776613875</v>
       </c>
       <c r="AK16">
-        <v>-0.0838287752675386</v>
+        <v>0.5421657064934461</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="AM16">
-        <v>-0.351</v>
+        <v>0.022</v>
+      </c>
+      <c r="AN16">
+        <v>607.4712643678162</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>568.9587136668206</v>
       </c>
       <c r="AQ16">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.289</v>
+        <v>0.0722</v>
       </c>
       <c r="E17">
-        <v>0.9940000000000001</v>
+        <v>0.216</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2412,19 +2412,19 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>25.7</v>
+        <v>19.9</v>
       </c>
       <c r="L17">
-        <v>0.3458950201884253</v>
+        <v>0.373358348968105</v>
       </c>
       <c r="M17">
-        <v>0.013</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>6.612410986775178e-05</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>0.0005058365758754864</v>
+        <v>-0</v>
       </c>
       <c r="P17">
         <v>-0</v>
@@ -2436,66 +2436,533 @@
         <v>-0</v>
       </c>
       <c r="S17">
-        <v>0.013</v>
-      </c>
-      <c r="T17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>26.8</v>
+        <v>2.27</v>
       </c>
       <c r="V17">
-        <v>0.1363173957273652</v>
+        <v>0.005573287503068991</v>
       </c>
       <c r="W17">
-        <v>0.1807313642756681</v>
+        <v>0.124375</v>
       </c>
       <c r="X17">
-        <v>0.1534783973810027</v>
+        <v>0.09417583106230437</v>
       </c>
       <c r="Y17">
-        <v>0.02725296689466533</v>
+        <v>0.03019916893769561</v>
       </c>
       <c r="Z17">
-        <v>0.1713244788784357</v>
+        <v>0.1202074875958502</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.1044960213904922</v>
+        <v>0.08261003917399803</v>
       </c>
       <c r="AC17">
-        <v>-0.1044960213904922</v>
+        <v>-0.08261003917399803</v>
       </c>
       <c r="AD17">
-        <v>310.2</v>
+        <v>300</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>310.2</v>
+        <v>300</v>
       </c>
       <c r="AG17">
-        <v>283.4</v>
+        <v>297.73</v>
       </c>
       <c r="AH17">
-        <v>0.6120757695343331</v>
+        <v>0.4241481690937368</v>
       </c>
       <c r="AI17">
-        <v>0.659719268396427</v>
+        <v>0.5996402158704777</v>
       </c>
       <c r="AJ17">
-        <v>0.5904166666666666</v>
+        <v>0.4222940867764493</v>
       </c>
       <c r="AK17">
-        <v>0.6391520072169599</v>
+        <v>0.5978153926470293</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
+        <v>-0.032</v>
+      </c>
+      <c r="AQ17">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bao Viet Securities Joint Stock Company (HNX:BVS)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.07290000000000001</v>
+      </c>
+      <c r="E18">
+        <v>0.09420000000000001</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>7.73</v>
+      </c>
+      <c r="L18">
+        <v>0.2712280701754386</v>
+      </c>
+      <c r="M18">
+        <v>2.34</v>
+      </c>
+      <c r="N18">
+        <v>0.03111702127659574</v>
+      </c>
+      <c r="O18">
+        <v>0.3027166882276843</v>
+      </c>
+      <c r="P18">
+        <v>2.34</v>
+      </c>
+      <c r="Q18">
+        <v>0.03111702127659574</v>
+      </c>
+      <c r="R18">
+        <v>0.3027166882276843</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0.217</v>
+      </c>
+      <c r="V18">
+        <v>0.00288563829787234</v>
+      </c>
+      <c r="W18">
+        <v>0.08365800865800865</v>
+      </c>
+      <c r="X18">
+        <v>0.0996659436058997</v>
+      </c>
+      <c r="Y18">
+        <v>-0.01600793494789104</v>
+      </c>
+      <c r="Z18">
+        <v>0.2127977301575449</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.08384999245343358</v>
+      </c>
+      <c r="AC18">
+        <v>-0.08384999245343358</v>
+      </c>
+      <c r="AD18">
+        <v>70.2</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>70.2</v>
+      </c>
+      <c r="AG18">
+        <v>69.983</v>
+      </c>
+      <c r="AH18">
+        <v>0.4828060522696011</v>
+      </c>
+      <c r="AI18">
+        <v>0.4211157768446311</v>
+      </c>
+      <c r="AJ18">
+        <v>0.4820330203949499</v>
+      </c>
+      <c r="AK18">
+        <v>0.420361238084369</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1.35</v>
+      </c>
+      <c r="AQ18">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VNDIRECT Securities Joint Stock Company (HOSE:VND)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.309</v>
+      </c>
+      <c r="E19">
+        <v>0.199</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>-0.005430257378300577</v>
+      </c>
+      <c r="J19">
+        <v>-0.004315436327126287</v>
+      </c>
+      <c r="K19">
+        <v>48</v>
+      </c>
+      <c r="L19">
+        <v>0.2368031573754317</v>
+      </c>
+      <c r="M19">
+        <v>4.8712</v>
+      </c>
+      <c r="N19">
+        <v>0.004384518451845184</v>
+      </c>
+      <c r="O19">
+        <v>0.1014833333333333</v>
+      </c>
+      <c r="P19">
+        <v>4.8712</v>
+      </c>
+      <c r="Q19">
+        <v>0.004384518451845184</v>
+      </c>
+      <c r="R19">
+        <v>0.1014833333333333</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>110.8</v>
+      </c>
+      <c r="V19">
+        <v>0.09972997299729973</v>
+      </c>
+      <c r="W19">
+        <v>0.0784698381559588</v>
+      </c>
+      <c r="X19">
+        <v>0.09788737724610702</v>
+      </c>
+      <c r="Y19">
+        <v>-0.01941753909014822</v>
+      </c>
+      <c r="Z19">
+        <v>0.1560417207424253</v>
+      </c>
+      <c r="AA19">
+        <v>-0.0006733881102391575</v>
+      </c>
+      <c r="AB19">
+        <v>0.08347690552566235</v>
+      </c>
+      <c r="AC19">
+        <v>-0.08415029363590151</v>
+      </c>
+      <c r="AD19">
+        <v>960.7</v>
+      </c>
+      <c r="AE19">
+        <v>5.543565852907635</v>
+      </c>
+      <c r="AF19">
+        <v>966.2435658529076</v>
+      </c>
+      <c r="AG19">
+        <v>855.4435658529077</v>
+      </c>
+      <c r="AH19">
+        <v>0.4651566054826951</v>
+      </c>
+      <c r="AI19">
+        <v>0.5988332675369432</v>
+      </c>
+      <c r="AJ19">
+        <v>0.4350206538888774</v>
+      </c>
+      <c r="AK19">
+        <v>0.5692545190618642</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1.21</v>
+      </c>
+      <c r="AN19">
+        <v>120087.5</v>
+      </c>
+      <c r="AP19">
+        <v>106930.4457316135</v>
+      </c>
+      <c r="AQ19">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tien Phong Securities Corporation (HOSE:ORS)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>1.744</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>6.44</v>
+      </c>
+      <c r="L20">
+        <v>0.06338582677165355</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>-0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>-0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>61.7</v>
+      </c>
+      <c r="V20">
+        <v>0.4426111908177905</v>
+      </c>
+      <c r="W20">
+        <v>0.06618705035971223</v>
+      </c>
+      <c r="X20">
+        <v>0.1048187922297877</v>
+      </c>
+      <c r="Y20">
+        <v>-0.03863174187007548</v>
+      </c>
+      <c r="Z20">
+        <v>0.4518366983901094</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.08480401806398581</v>
+      </c>
+      <c r="AC20">
+        <v>-0.08480401806398581</v>
+      </c>
+      <c r="AD20">
+        <v>155.9</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>155.9</v>
+      </c>
+      <c r="AG20">
+        <v>94.2</v>
+      </c>
+      <c r="AH20">
+        <v>0.5279376904842533</v>
+      </c>
+      <c r="AI20">
+        <v>0.6044978673904615</v>
+      </c>
+      <c r="AJ20">
+        <v>0.4032534246575342</v>
+      </c>
+      <c r="AK20">
+        <v>0.4801223241590215</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-0.066</v>
+      </c>
+      <c r="AQ20">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Petrovietnam Securities Incorporated (HNX:PSI)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>-0</v>
+      </c>
+      <c r="N21">
+        <v>-0</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>1.02</v>
+      </c>
+      <c r="V21">
+        <v>0.04722222222222222</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0.1070685954740598</v>
+      </c>
+      <c r="Y21">
+        <v>-0.1070685954740598</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.08517025647850503</v>
+      </c>
+      <c r="AC21">
+        <v>-0.08517025647850503</v>
+      </c>
+      <c r="AD21">
+        <v>25.9</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>25.9</v>
+      </c>
+      <c r="AG21">
+        <v>24.88</v>
+      </c>
+      <c r="AH21">
+        <v>0.5452631578947368</v>
+      </c>
+      <c r="AI21">
+        <v>0.4778597785977859</v>
+      </c>
+      <c r="AJ21">
+        <v>0.5352839931153184</v>
+      </c>
+      <c r="AK21">
+        <v>0.4678450545317788</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
         <v>0</v>
       </c>
     </row>
